--- a/strategy_packs/momentum_senales.xlsx
+++ b/strategy_packs/momentum_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Momentum clásico: el retorno % del último año mapeado linealmente a score. −20% o peor → −100; +30% → 0; +80% o más → +100.</t>
+          <t>Momentum clasico: el retorno % del ultimo anio mapeado linealmente a score. -20% o peor -&gt; -100; +30% -&gt; 0; +80% o mas -&gt; +100.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -493,6 +493,230 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>{"min": -20.0, "max": 80.0, "clamp": true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fuerza_relativa_52w</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fuerza relativa 52 semanas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Premia a los activos que le vienen ganando a su benchmark en la ventana de 52 semanas: &gt;20 puntos de ventaja -&gt; 100; positivo -&gt; 50; resto -&gt; -50.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>relative_strength_52w</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>alineacion_timeframes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alineación de timeframes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Promedio de las tendencias diaria, semanal y mensual: alto solo cuando los tres marcos coinciden.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>{"components": [{"signal_key": "tendencia_d", "weight": 1}, {"signal_key": "tendencia_w", "weight": 1}, {"signal_key": "tendencia_m", "weight": 1}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tendencia_d</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tendencia diaria</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mapa del regimen de tendencia diario a score (alcista fuerte 100 ... bajista fuerte -100).</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>trend_daily</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tendencia_w</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tendencia semanal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mapa del regimen de tendencia semanal a score (dependencia de alineacion_timeframes).</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>trend_weekly</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tendencia_m</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tendencia mensual</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mapa del regimen de tendencia mensual a score.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>trend_monthly</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dist_sma_d</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Distancia SMA diaria (z-score)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Distancia a la SMA optima diaria en desvios: -3 -&gt; -100, +3 -&gt; +100 (premia estar extendido por arriba).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dist_optimal_sma_daily</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>{"min": -3.0, "max": 3.0, "clamp": true}</t>
         </is>
       </c>
     </row>

--- a/strategy_packs/momentum_senales.xlsx
+++ b/strategy_packs/momentum_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>params</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>publica</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,7 +484,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>return_52w</t>
@@ -493,6 +497,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>{"min": -20.0, "max": 80.0, "clamp": true}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -517,7 +526,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>relative_strength_52w</t>
@@ -531,6 +539,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -555,8 +568,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>composite</t>
@@ -565,6 +576,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>{"components": [{"signal_key": "tendencia_d", "weight": 1}, {"signal_key": "tendencia_w", "weight": 1}, {"signal_key": "tendencia_m", "weight": 1}]}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -589,7 +605,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>trend_daily</t>
@@ -603,6 +618,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -627,7 +647,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>trend_weekly</t>
@@ -641,6 +660,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -665,7 +689,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>trend_monthly</t>
@@ -679,6 +702,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -703,7 +731,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>dist_optimal_sma_daily</t>
@@ -717,6 +744,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>{"min": -3.0, "max": 3.0, "clamp": true}</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>

--- a/strategy_packs/momentum_senales.xlsx
+++ b/strategy_packs/momentum_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,17 +550,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alineacion_timeframes</t>
+          <t>tendencia_d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alineación de timeframes</t>
+          <t>Tendencia diaria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Promedio de las tendencias diaria, semanal y mensual: alto solo cuando los tres marcos coinciden.</t>
+          <t>Mapa del regimen de tendencia diario a score (alcista fuerte 100 ... bajista fuerte -100).</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -568,14 +568,19 @@
           <t>asset</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>trend_daily</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>discrete_map</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>{"components": [{"signal_key": "tendencia_d", "weight": 1}, {"signal_key": "tendencia_w", "weight": 1}, {"signal_key": "tendencia_m", "weight": 1}]}</t>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -587,17 +592,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tendencia_d</t>
+          <t>tendencia_w</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tendencia diaria</t>
+          <t>Tendencia semanal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mapa del regimen de tendencia diario a score (alcista fuerte 100 ... bajista fuerte -100).</t>
+          <t>Mapa del regimen de tendencia semanal a score.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -607,7 +612,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>trend_daily</t>
+          <t>trend_weekly</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -629,17 +634,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tendencia_w</t>
+          <t>tendencia_m</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tendencia semanal</t>
+          <t>Tendencia mensual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mapa del regimen de tendencia semanal a score (dependencia de alineacion_timeframes).</t>
+          <t>Mapa del regimen de tendencia mensual a score.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -649,7 +654,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>trend_weekly</t>
+          <t>trend_monthly</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -671,17 +676,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tendencia_m</t>
+          <t>dist_sma_d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tendencia mensual</t>
+          <t>Distancia SMA diaria (z-score)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mapa del regimen de tendencia mensual a score.</t>
+          <t>Distancia a la SMA optima diaria en desvios: -3 -&gt; -100, +3 -&gt; +100 (premia estar extendido por arriba).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -691,62 +696,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>trend_monthly</t>
+          <t>dist_optimal_sma_daily</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>discrete_map</t>
+          <t>range</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+          <t>{"min": -3.0, "max": 3.0, "clamp": true}</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dist_sma_d</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Distancia SMA diaria (z-score)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Distancia a la SMA optima diaria en desvios: -3 -&gt; -100, +3 -&gt; +100 (premia estar extendido por arriba).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>asset</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>dist_optimal_sma_daily</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>{"min": -3.0, "max": 3.0, "clamp": true}</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>si</t>
         </is>

--- a/strategy_packs/momentum_senales.xlsx
+++ b/strategy_packs/momentum_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,30 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>indicator_key</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>group_type</t>
+          <t>formula_type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>indicator_key</t>
+          <t>params</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>formula_type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>params</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>publica</t>
         </is>
@@ -481,25 +471,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>return_52w</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>range</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>return_52w</t>
+          <t>{"min": -20.0, "max": 80.0, "clamp": true}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>{"min": -20.0, "max": 80.0, "clamp": true}</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -523,25 +508,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>relative_strength_52w</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>threshold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>relative_strength_52w</t>
+          <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -565,25 +545,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>trend_daily</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>trend_daily</t>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>discrete_map</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -607,25 +582,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>trend_weekly</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>trend_weekly</t>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>discrete_map</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -649,25 +619,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>trend_monthly</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>trend_monthly</t>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>discrete_map</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -691,25 +656,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>dist_optimal_sma_daily</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>range</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>dist_optimal_sma_daily</t>
+          <t>{"min": -3.0, "max": 3.0, "clamp": true}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>{"min": -3.0, "max": 3.0, "clamp": true}</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
